--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F7105FA-96F3-4165-BD4D-16AE6BEDB094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E618D1C-DA77-4D41-9B56-C02ADC3ED6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="112">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -374,6 +374,12 @@
   </si>
   <si>
     <t>T-014</t>
+  </si>
+  <si>
+    <t>T-009</t>
+  </si>
+  <si>
+    <t>T-007</t>
   </si>
 </sst>
 </file>
@@ -1132,11 +1138,11 @@
         <v>55.919999999999959</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M8">
         <f>SUMIF(Executions!B:B,A8,Executions!H:H)</f>
-        <v>0</v>
+        <v>-28.16999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1222,11 +1228,11 @@
         <v>43.539999999999992</v>
       </c>
       <c r="L10" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M10">
         <f>SUMIF(Executions!B:B,A10,Executions!H:H)</f>
-        <v>0</v>
+        <v>-25.445000000000011</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1492,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1564,7 +1570,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A9" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A11" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1771,8 +1777,9 @@
       <c r="C9" s="1">
         <v>46087</v>
       </c>
-      <c r="D9" t="s">
-        <v>108</v>
+      <c r="D9" t="str">
+        <f>VLOOKUP(B9,Trades!A$1:M100007,3,FALSE)</f>
+        <v>LULU</v>
       </c>
       <c r="E9" t="s">
         <v>64</v>
@@ -1792,12 +1799,78 @@
         <v>-0.71825396825396837</v>
       </c>
     </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46087</v>
+      </c>
+      <c r="D10" t="str">
+        <f>VLOOKUP(B10,Trades!A$1:M100008,3,FALSE)</f>
+        <v>UUUU</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10">
+        <v>18.824999999999999</v>
+      </c>
+      <c r="G10">
+        <v>7</v>
+      </c>
+      <c r="H10">
+        <f>IF(VLOOKUP(B10,Trades!A:M,4,FALSE)="Long",(F10-VLOOKUP(B10,Trades!A:M,6,FALSE))*G10,(VLOOKUP(B10,Trades!A:M,6,FALSE)-F10)*G10)</f>
+        <v>-25.445000000000011</v>
+      </c>
+      <c r="I10">
+        <f>H10/Trades!I10</f>
+        <v>-1.1688102893890682</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46087</v>
+      </c>
+      <c r="D11" t="str">
+        <f>VLOOKUP(B11,Trades!A$1:M100009,3,FALSE)</f>
+        <v>OKLO</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11">
+        <v>58.43</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <f>IF(VLOOKUP(B11,Trades!A:M,4,FALSE)="Long",(F11-VLOOKUP(B11,Trades!A:M,6,FALSE))*G11,(VLOOKUP(B11,Trades!A:M,6,FALSE)-F11)*G11)</f>
+        <v>-28.16999999999998</v>
+      </c>
+      <c r="I11">
+        <f>H11/Trades!I11</f>
+        <v>-1.2570281124497982</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100009</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100011</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E9" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E11" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2121,7 +2194,7 @@
       </c>
       <c r="D9">
         <f>COUNTIFS(Trades!E:E, A9, Trades!M:M, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <f>IFERROR(C9/B9,0)</f>
@@ -2129,19 +2202,19 @@
       </c>
       <c r="F9">
         <f>SUMIF(Trades!E:E,A9,Trades!M:M)</f>
-        <v>87.110000000000056</v>
+        <v>61.665000000000049</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>17.422000000000011</v>
+        <v>12.333000000000009</v>
       </c>
       <c r="H9">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M,"&lt;0")),0)</f>
-        <v>0</v>
+        <v>3.4234623698172535</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>17.422000000000011</v>
+        <v>12.333000000000009</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2158,7 +2231,7 @@
       </c>
       <c r="D10">
         <f>COUNTIFS(Trades!E:E, A10, Trades!M:M, "&lt;0")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10">
         <f>IFERROR(C10/B10,0)</f>
@@ -2166,11 +2239,11 @@
       </c>
       <c r="F10">
         <f>SUMIF(Trades!E:E,A10,Trades!M:M)</f>
-        <v>-55.721999999999952</v>
+        <v>-83.891999999999939</v>
       </c>
       <c r="G10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-11.14439999999999</v>
+        <v>-16.778399999999987</v>
       </c>
       <c r="H10">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M,"&lt;0")),0)</f>
@@ -2178,7 +2251,7 @@
       </c>
       <c r="I10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-11.14439999999999</v>
+        <v>-16.778399999999987</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2526,7 +2599,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>8.2227142857143054</v>
+        <v>4.3930714285714485</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2535,7 +2608,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>115.11800000000028</v>
+        <v>61.503000000000284</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2544,7 +2617,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>1.4840424607793723</v>
+        <v>2.7777506788286654</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2567,7 +2640,7 @@
       </c>
       <c r="B10">
         <f>MIN(Trades!M:M)</f>
-        <v>-23.399999999999981</v>
+        <v>-28.16999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2585,7 +2658,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-18.573999999999984</v>
+        <v>-21.867399999999989</v>
       </c>
     </row>
   </sheetData>

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E618D1C-DA77-4D41-9B56-C02ADC3ED6D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5D28D1-366C-444E-AD08-4BB50B8E63E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="116">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -380,6 +380,18 @@
   </si>
   <si>
     <t>T-007</t>
+  </si>
+  <si>
+    <t>T-003</t>
+  </si>
+  <si>
+    <t>IHS</t>
+  </si>
+  <si>
+    <t>AVBP</t>
+  </si>
+  <si>
+    <t>Short Squeeze</t>
   </si>
 </sst>
 </file>
@@ -427,7 +439,74 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -778,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -832,7 +911,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A15" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
+        <f t="shared" ref="A2:A17" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
         <v>T-001</v>
       </c>
       <c r="B2" s="1">
@@ -857,7 +936,7 @@
         <v>18</v>
       </c>
       <c r="I2">
-        <f t="shared" ref="I2:I15" si="1">IF(D2="Long",(F2-G2)*H2,(G2-F2)*0)</f>
+        <f t="shared" ref="I2:I16" si="1">IF(D2="Long",(F2-G2)*H2,(G2-F2)*0)</f>
         <v>23.399999999999981</v>
       </c>
       <c r="J2">
@@ -909,7 +988,7 @@
         <v>2</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K15" si="2">I3*J3</f>
+        <f t="shared" ref="K3:K16" si="2">I3*J3</f>
         <v>43.919999999999987</v>
       </c>
       <c r="L3" t="s">
@@ -958,11 +1037,11 @@
         <v>57.95999999999998</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M4">
         <f>SUMIF(Executions!B:B,A4,Executions!H:H)</f>
-        <v>0</v>
+        <v>-35.010000000000005</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1460,12 +1539,105 @@
         <v>-21.71999999999997</v>
       </c>
     </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f t="shared" si="0"/>
+        <v>T-015</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16">
+        <v>8.16</v>
+      </c>
+      <c r="G16">
+        <v>7.84</v>
+      </c>
+      <c r="H16">
+        <v>50</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="1"/>
+        <v>16.000000000000014</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>32.000000000000028</v>
+      </c>
+      <c r="L16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16">
+        <f>SUMIF(Executions!B:B,A16,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="str">
+        <f t="shared" si="0"/>
+        <v>T-016</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17">
+        <v>24.88</v>
+      </c>
+      <c r="G17">
+        <v>22.31</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ref="I17" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
+        <v>10.280000000000001</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17">
+        <f t="shared" ref="K17" si="4">I17*J17</f>
+        <v>20.560000000000002</v>
+      </c>
+      <c r="L17" t="s">
+        <v>30</v>
+      </c>
+      <c r="M17">
+        <f>SUMIF(Executions!B:B,A17,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M15">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>K2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>K2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1473,7 +1645,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7CC3C28F-4F55-4478-BFCD-3E2D4B39BBC5}">
       <formula1>"Long,Short"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E16:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E18:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
       <formula1>"Breakout,Pullback,Range Break,Reversal,Earning Play, A+ Setup,Buy the Dip, Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{F4069621-A7E8-45FE-9BEB-689DCD314A70}">
@@ -1481,14 +1653,21 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F958648C-BDD0-4279-9367-17373A7E8527}">
           <x14:formula1>
-            <xm:f>Setups!$A$2:$A$11</xm:f>
+            <xm:f>Setups!$A$2:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E15</xm:sqref>
+          <xm:sqref>E3:E17</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35AFC476-A1FB-4896-88D9-082697747CAE}">
+          <x14:formula1>
+            <xm:f>Setups!$A$2:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1498,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1570,7 +1749,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A11" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A12" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1865,12 +2044,45 @@
         <v>-1.2570281124497982</v>
       </c>
     </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46090</v>
+      </c>
+      <c r="D12" t="str">
+        <f>VLOOKUP(B12,Trades!A$1:M100010,3,FALSE)</f>
+        <v>TMDX</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12">
+        <v>125.27</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12">
+        <f>IF(VLOOKUP(B12,Trades!A:M,4,FALSE)="Long",(F12-VLOOKUP(B12,Trades!A:M,6,FALSE))*G12,(VLOOKUP(B12,Trades!A:M,6,FALSE)-F12)*G12)</f>
+        <v>-35.010000000000005</v>
+      </c>
+      <c r="I12">
+        <f>H12/Trades!I12</f>
+        <v>-3.4526627218934962</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100011</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100012</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E11" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E12" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1880,7 +2092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88D4C81-5CF1-4DFA-99E6-729F5B0DC763}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1935,7 +2147,7 @@
       </c>
       <c r="D2">
         <f>COUNTIFS(Trades!E:E, A2, Trades!M:M, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <f>IFERROR(C2/B2,0)</f>
@@ -1943,19 +2155,19 @@
       </c>
       <c r="F2">
         <f>SUMIF(Trades!E:E,A2,Trades!M:M)</f>
-        <v>83.73000000000016</v>
+        <v>48.720000000000155</v>
       </c>
       <c r="G2">
         <f>IFERROR(F2/B2,0)</f>
-        <v>27.910000000000053</v>
+        <v>16.240000000000052</v>
       </c>
       <c r="H2">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A2, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M,Trades!E:E, A2,Trades!M:M,"&lt;0")),0)</f>
-        <v>0</v>
+        <v>2.3916023993144857</v>
       </c>
       <c r="I2">
         <f>IFERROR(F2/B2,0)</f>
-        <v>27.910000000000053</v>
+        <v>16.240000000000052</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1975,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E11" si="0">IFERROR(C3/B3,0)</f>
+        <f t="shared" ref="E3:E12" si="0">IFERROR(C3/B3,0)</f>
         <v>0</v>
       </c>
       <c r="F3">
@@ -1983,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G11" si="1">IFERROR(F3/B3,0)</f>
+        <f t="shared" ref="G3:G12" si="1">IFERROR(F3/B3,0)</f>
         <v>0</v>
       </c>
       <c r="H3">
@@ -1991,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I11" si="2">IFERROR(F3/B3,0)</f>
+        <f t="shared" ref="I3:I12" si="2">IFERROR(F3/B3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2186,7 +2398,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Trades!E:E,A9)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <f>COUNTIFS(Trades!E:E, A9,Trades!M:M, "&gt;0")</f>
@@ -2198,7 +2410,7 @@
       </c>
       <c r="E9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.4</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F9">
         <f>SUMIF(Trades!E:E,A9,Trades!M:M)</f>
@@ -2206,7 +2418,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>12.333000000000009</v>
+        <v>10.277500000000009</v>
       </c>
       <c r="H9">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M,"&lt;0")),0)</f>
@@ -2214,7 +2426,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>12.333000000000009</v>
+        <v>10.277500000000009</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2256,11 +2468,11 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="B11">
         <f>COUNTIF(Trades!E:E,A11)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <f>COUNTIFS(Trades!E:E, A11,Trades!M:M, "&gt;0")</f>
@@ -2271,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
+        <f>IFERROR(C11/B11,0)</f>
         <v>0</v>
       </c>
       <c r="F11">
@@ -2279,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <f t="shared" si="1"/>
+        <f>IFERROR(F11/B11,0)</f>
         <v>0</v>
       </c>
       <c r="H11">
@@ -2287,6 +2499,43 @@
         <v>0</v>
       </c>
       <c r="I11">
+        <f>IFERROR(F11/B11,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12">
+        <f>COUNTIF(Trades!E:E,A12)</f>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(Trades!E:E, A12,Trades!M:M, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f>COUNTIFS(Trades!E:E, A12, Trades!M:M, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>SUMIF(Trades!E:E,A12,Trades!M:M)</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M,"&lt;0")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2581,7 +2830,7 @@
       </c>
       <c r="B2">
         <f>COUNTA(Trades!A:A)-1</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2590,7 +2839,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Trades!M:M,"&gt;0")/COUNT(Trades!M:M)</f>
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2599,7 +2848,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>4.3930714285714485</v>
+        <v>1.6558125000000166</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2608,7 +2857,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>61.503000000000284</v>
+        <v>26.493000000000265</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2617,7 +2866,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>2.7777506788286654</v>
+        <v>6.4484958290868715</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2640,7 +2889,7 @@
       </c>
       <c r="B10">
         <f>MIN(Trades!M:M)</f>
-        <v>-28.16999999999998</v>
+        <v>-35.010000000000005</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2658,7 +2907,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-21.867399999999989</v>
+        <v>-24.057833333333321</v>
       </c>
     </row>
   </sheetData>

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5D28D1-366C-444E-AD08-4BB50B8E63E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796865A4-D3BB-46C7-8C39-23BB42F6FC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="116">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -439,7 +439,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -464,66 +464,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -857,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -911,7 +851,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A17" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
+        <f t="shared" ref="A2:A18" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
         <v>T-001</v>
       </c>
       <c r="B2" s="1">
@@ -1611,14 +1551,14 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
+        <f t="shared" ref="I17:I18" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
         <v>10.280000000000001</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17">
-        <f t="shared" ref="K17" si="4">I17*J17</f>
+        <f t="shared" ref="K17:K18" si="4">I17*J17</f>
         <v>20.560000000000002</v>
       </c>
       <c r="L17" t="s">
@@ -1629,8 +1569,53 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="str">
+        <f t="shared" si="0"/>
+        <v>T-017</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18">
+        <v>77.150000000000006</v>
+      </c>
+      <c r="G18">
+        <v>74.31</v>
+      </c>
+      <c r="H18">
+        <v>20</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="3"/>
+        <v>56.800000000000068</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="4"/>
+        <v>113.60000000000014</v>
+      </c>
+      <c r="L18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18">
+        <f>SUMIF(Executions!B:B,A18,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M17">
+  <conditionalFormatting sqref="M2:M18">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -1645,7 +1630,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7CC3C28F-4F55-4478-BFCD-3E2D4B39BBC5}">
       <formula1>"Long,Short"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E18:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E19:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
       <formula1>"Breakout,Pullback,Range Break,Reversal,Earning Play, A+ Setup,Buy the Dip, Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{F4069621-A7E8-45FE-9BEB-689DCD314A70}">
@@ -1661,7 +1646,7 @@
           <x14:formula1>
             <xm:f>Setups!$A$2:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E17</xm:sqref>
+          <xm:sqref>E3:E18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35AFC476-A1FB-4896-88D9-082697747CAE}">
           <x14:formula1>
@@ -2361,7 +2346,7 @@
       </c>
       <c r="B8">
         <f>COUNTIF(Trades!E:E,A8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <f>COUNTIFS(Trades!E:E, A8,Trades!M:M, "&gt;0")</f>
@@ -2830,7 +2815,7 @@
       </c>
       <c r="B2">
         <f>COUNTA(Trades!A:A)-1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2839,7 +2824,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Trades!M:M,"&gt;0")/COUNT(Trades!M:M)</f>
-        <v>0.25</v>
+        <v>0.23529411764705882</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2848,7 +2833,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>1.6558125000000166</v>
+        <v>1.5584117647058979</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796865A4-D3BB-46C7-8C39-23BB42F6FC4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACB4C0D-14DC-4C26-95C7-AF9BBD5ED4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>Short Squeeze</t>
+  </si>
+  <si>
+    <t>T-012</t>
   </si>
 </sst>
 </file>
@@ -1382,11 +1385,11 @@
         <v>43.679999999999964</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M13">
         <f>SUMIF(Executions!B:B,A13,Executions!H:H)</f>
-        <v>0</v>
+        <v>-24.779999999999976</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -1662,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1734,7 +1737,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A12" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A14" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2062,12 +2065,59 @@
         <v>-3.4526627218934962</v>
       </c>
     </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D13" t="str">
+        <f>VLOOKUP(B13,Trades!A$1:M100011,3,FALSE)</f>
+        <v>APPS</v>
+      </c>
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13">
+        <v>3.68</v>
+      </c>
+      <c r="G13">
+        <v>42</v>
+      </c>
+      <c r="H13">
+        <f>IF(VLOOKUP(B13,Trades!A:M,4,FALSE)="Long",(F13-VLOOKUP(B13,Trades!A:M,6,FALSE))*G13,(VLOOKUP(B13,Trades!A:M,6,FALSE)-F13)*G13)</f>
+        <v>-24.779999999999976</v>
+      </c>
+      <c r="I13">
+        <f>H13/Trades!I13</f>
+        <v>-1.1346153846153844</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="H14" t="e">
+        <f>IF(VLOOKUP(B14,Trades!A:M,4,FALSE)="Long",(F14-VLOOKUP(B14,Trades!A:M,6,FALSE))*G14,(VLOOKUP(B14,Trades!A:M,6,FALSE)-F14)*G14)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" t="e">
+        <f>H14/Trades!I14</f>
+        <v>#N/A</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100012</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100013</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E12" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E13" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2428,7 +2478,7 @@
       </c>
       <c r="D10">
         <f>COUNTIFS(Trades!E:E, A10, Trades!M:M, "&lt;0")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <f>IFERROR(C10/B10,0)</f>
@@ -2436,11 +2486,11 @@
       </c>
       <c r="F10">
         <f>SUMIF(Trades!E:E,A10,Trades!M:M)</f>
-        <v>-83.891999999999939</v>
+        <v>-108.67199999999991</v>
       </c>
       <c r="G10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-16.778399999999987</v>
+        <v>-21.734399999999983</v>
       </c>
       <c r="H10">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M,"&lt;0")),0)</f>
@@ -2448,7 +2498,7 @@
       </c>
       <c r="I10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-16.778399999999987</v>
+        <v>-21.734399999999983</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2833,7 +2883,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>1.5584117647058979</v>
+        <v>0.10076470588236992</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2842,7 +2892,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>26.493000000000265</v>
+        <v>1.7130000000002887</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2851,7 +2901,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>6.4484958290868715</v>
+        <v>99.731465265599184</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2892,7 +2942,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-24.057833333333321</v>
+        <v>-24.160999999999991</v>
       </c>
     </row>
   </sheetData>

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DACB4C0D-14DC-4C26-95C7-AF9BBD5ED4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7CB5E2-04F4-465A-82C7-7FAAA2F72F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -395,6 +395,42 @@
   </si>
   <si>
     <t>T-012</t>
+  </si>
+  <si>
+    <t>T-015</t>
+  </si>
+  <si>
+    <t>IHS is showing a recovery but todays earnings were negative I decided to exit before any negative move might happen if I lose the trend, be it, there is too much risk in current market environment</t>
+  </si>
+  <si>
+    <t>The war in Iran has caused the oil to pike and the market to go down, until last Friday, there were 6 consecutive red days for the main indexes in the market, it clearly hit me hard</t>
+  </si>
+  <si>
+    <t>I have trading really few regarding the last drops that the market has experienced, I feel really down, but I am avoiding any behavior that could compromise my capital</t>
+  </si>
+  <si>
+    <t>BDX</t>
+  </si>
+  <si>
+    <t>Mean reversion</t>
+  </si>
+  <si>
+    <t>QBTS</t>
+  </si>
+  <si>
+    <t>T-019</t>
+  </si>
+  <si>
+    <t>T-016</t>
+  </si>
+  <si>
+    <t>XLE</t>
+  </si>
+  <si>
+    <t>T-018</t>
+  </si>
+  <si>
+    <t>The market is really choppy and I didn't wait for confirmation, at the end, what it was looking as a potential bounce, finish by falling back, and not recovering.</t>
   </si>
 </sst>
 </file>
@@ -430,14 +466,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -800,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -854,7 +889,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A18" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
+        <f t="shared" ref="A2:A21" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
         <v>T-001</v>
       </c>
       <c r="B2" s="1">
@@ -1520,11 +1555,11 @@
         <v>32.000000000000028</v>
       </c>
       <c r="L16" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M16">
         <f>SUMIF(Executions!B:B,A16,Executions!H:H)</f>
-        <v>0</v>
+        <v>0.99999999999997868</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -1554,14 +1589,14 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I18" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
+        <f t="shared" ref="I17:I21" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
         <v>10.280000000000001</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17">
-        <f t="shared" ref="K17:K18" si="4">I17*J17</f>
+        <f t="shared" ref="K17:K21" si="4">I17*J17</f>
         <v>20.560000000000002</v>
       </c>
       <c r="L17" t="s">
@@ -1569,7 +1604,7 @@
       </c>
       <c r="M17">
         <f>SUMIF(Executions!B:B,A17,Executions!H:H)</f>
-        <v>0</v>
+        <v>-9.5600000000000023</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1617,8 +1652,143 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="str">
+        <f t="shared" si="0"/>
+        <v>T-018</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19">
+        <v>162.47999999999999</v>
+      </c>
+      <c r="G19">
+        <v>156.29</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="3"/>
+        <v>18.569999999999993</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="4"/>
+        <v>37.139999999999986</v>
+      </c>
+      <c r="L19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19">
+        <f>SUMIF(Executions!B:B,A19,Executions!H:H)</f>
+        <v>-19.70999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
+        <f t="shared" si="0"/>
+        <v>T-019</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20">
+        <v>20.83</v>
+      </c>
+      <c r="G20">
+        <v>16.91</v>
+      </c>
+      <c r="H20">
+        <v>8</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="3"/>
+        <v>31.359999999999985</v>
+      </c>
+      <c r="J20">
+        <v>2</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="4"/>
+        <v>62.71999999999997</v>
+      </c>
+      <c r="L20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20">
+        <f>SUMIF(Executions!B:B,A20,Executions!H:H)</f>
+        <v>-31.359999999999985</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f t="shared" si="0"/>
+        <v>T-020</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21">
+        <v>58.85</v>
+      </c>
+      <c r="G21">
+        <v>57.24</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="3"/>
+        <v>6.4399999999999977</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="4"/>
+        <v>12.879999999999995</v>
+      </c>
+      <c r="L21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21">
+        <f>SUMIF(Executions!B:B,A21,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M18">
+  <conditionalFormatting sqref="M2:M21">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -1633,7 +1803,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7CC3C28F-4F55-4478-BFCD-3E2D4B39BBC5}">
       <formula1>"Long,Short"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E19:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E22:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
       <formula1>"Breakout,Pullback,Range Break,Reversal,Earning Play, A+ Setup,Buy the Dip, Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{F4069621-A7E8-45FE-9BEB-689DCD314A70}">
@@ -1647,13 +1817,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F958648C-BDD0-4279-9367-17373A7E8527}">
           <x14:formula1>
-            <xm:f>Setups!$A$2:$A$12</xm:f>
+            <xm:f>Setups!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E18</xm:sqref>
+          <xm:sqref>E3:E21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35AFC476-A1FB-4896-88D9-082697747CAE}">
           <x14:formula1>
-            <xm:f>Setups!$A$2:$A$13</xm:f>
+            <xm:f>Setups!$A$2:$A$14</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
@@ -1665,7 +1835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1737,7 +1907,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A14" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A17" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2103,21 +2273,136 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H14" t="e">
+      <c r="B14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46098</v>
+      </c>
+      <c r="D14" t="str">
+        <f>VLOOKUP(B14,Trades!A$1:M100012,3,FALSE)</f>
+        <v>IHS</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14">
+        <v>8.18</v>
+      </c>
+      <c r="G14">
+        <v>50</v>
+      </c>
+      <c r="H14">
         <f>IF(VLOOKUP(B14,Trades!A:M,4,FALSE)="Long",(F14-VLOOKUP(B14,Trades!A:M,6,FALSE))*G14,(VLOOKUP(B14,Trades!A:M,6,FALSE)-F14)*G14)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I14" t="e">
+        <v>0.99999999999997868</v>
+      </c>
+      <c r="I14">
         <f>H14/Trades!I14</f>
-        <v>#N/A</v>
+        <v>4.3687199650501496E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46099</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15">
+        <v>16.91</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+      <c r="H15">
+        <f>IF(VLOOKUP(B15,Trades!A:M,4,FALSE)="Long",(F15-VLOOKUP(B15,Trades!A:M,6,FALSE))*G15,(VLOOKUP(B15,Trades!A:M,6,FALSE)-F15)*G15)</f>
+        <v>-31.359999999999985</v>
+      </c>
+      <c r="I15">
+        <f>H15/Trades!I15</f>
+        <v>-1.4723004694835706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16">
+        <v>22.49</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <f>IF(VLOOKUP(B16,Trades!A:M,4,FALSE)="Long",(F16-VLOOKUP(B16,Trades!A:M,6,FALSE))*G16,(VLOOKUP(B16,Trades!A:M,6,FALSE)-F16)*G16)</f>
+        <v>-9.5600000000000023</v>
+      </c>
+      <c r="I16">
+        <f>H16/Trades!I16</f>
+        <v>-0.59749999999999959</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17">
+        <v>155.91</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17">
+        <f>IF(VLOOKUP(B17,Trades!A:M,4,FALSE)="Long",(F17-VLOOKUP(B17,Trades!A:M,6,FALSE))*G17,(VLOOKUP(B17,Trades!A:M,6,FALSE)-F17)*G17)</f>
+        <v>-19.70999999999998</v>
+      </c>
+      <c r="I17">
+        <f>H17/Trades!I17</f>
+        <v>-1.9173151750972741</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100013</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E18:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100017</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E13" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E17" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2127,7 +2412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88D4C81-5CF1-4DFA-99E6-729F5B0DC763}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -2222,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E12" si="0">IFERROR(C3/B3,0)</f>
+        <f t="shared" ref="E3:E13" si="0">IFERROR(C3/B3,0)</f>
         <v>0</v>
       </c>
       <c r="F3">
@@ -2230,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G12" si="1">IFERROR(F3/B3,0)</f>
+        <f t="shared" ref="G3:G13" si="1">IFERROR(F3/B3,0)</f>
         <v>0</v>
       </c>
       <c r="H3">
@@ -2238,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I12" si="2">IFERROR(F3/B3,0)</f>
+        <f t="shared" ref="I3:I13" si="2">IFERROR(F3/B3,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -2433,11 +2718,11 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Trades!E:E,A9)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <f>COUNTIFS(Trades!E:E, A9,Trades!M:M, "&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <f>COUNTIFS(Trades!E:E, A9, Trades!M:M, "&lt;0")</f>
@@ -2445,23 +2730,23 @@
       </c>
       <c r="E9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="F9">
         <f>SUMIF(Trades!E:E,A9,Trades!M:M)</f>
-        <v>61.665000000000049</v>
+        <v>62.665000000000028</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>10.277500000000009</v>
+        <v>8.9521428571428618</v>
       </c>
       <c r="H9">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M,"&lt;0")),0)</f>
-        <v>3.4234623698172535</v>
+        <v>3.4627628217724506</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>10.277500000000009</v>
+        <v>8.9521428571428618</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2470,7 +2755,7 @@
       </c>
       <c r="B10">
         <f>COUNTIF(Trades!E:E,A10)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <f>COUNTIFS(Trades!E:E, A10,Trades!M:M, "&gt;0")</f>
@@ -2478,7 +2763,7 @@
       </c>
       <c r="D10">
         <f>COUNTIFS(Trades!E:E, A10, Trades!M:M, "&lt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <f>IFERROR(C10/B10,0)</f>
@@ -2486,11 +2771,11 @@
       </c>
       <c r="F10">
         <f>SUMIF(Trades!E:E,A10,Trades!M:M)</f>
-        <v>-108.67199999999991</v>
+        <v>-140.0319999999999</v>
       </c>
       <c r="G10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-21.734399999999983</v>
+        <v>-23.338666666666651</v>
       </c>
       <c r="H10">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M,"&lt;0")),0)</f>
@@ -2498,7 +2783,7 @@
       </c>
       <c r="I10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-21.734399999999983</v>
+        <v>-23.338666666666651</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2515,7 +2800,7 @@
       </c>
       <c r="D11">
         <f>COUNTIFS(Trades!E:E, A11, Trades!M:M, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <f>IFERROR(C11/B11,0)</f>
@@ -2523,11 +2808,11 @@
       </c>
       <c r="F11">
         <f>SUMIF(Trades!E:E,A11,Trades!M:M)</f>
-        <v>0</v>
+        <v>-9.5600000000000023</v>
       </c>
       <c r="G11">
         <f>IFERROR(F11/B11,0)</f>
-        <v>0</v>
+        <v>-9.5600000000000023</v>
       </c>
       <c r="H11">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A11, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A11, Trades!M:M,"&lt;0")),0)</f>
@@ -2535,16 +2820,16 @@
       </c>
       <c r="I11">
         <f>IFERROR(F11/B11,0)</f>
-        <v>0</v>
+        <v>-9.5600000000000023</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>122</v>
       </c>
       <c r="B12">
         <f>COUNTIF(Trades!E:E,A12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <f>COUNTIFS(Trades!E:E, A12,Trades!M:M, "&gt;0")</f>
@@ -2552,25 +2837,62 @@
       </c>
       <c r="D12">
         <f>COUNTIFS(Trades!E:E, A12, Trades!M:M, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <f t="shared" si="0"/>
+        <f>IFERROR(C12/B12,0)</f>
         <v>0</v>
       </c>
       <c r="F12">
         <f>SUMIF(Trades!E:E,A12,Trades!M:M)</f>
-        <v>0</v>
+        <v>-19.70999999999998</v>
       </c>
       <c r="G12">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>IFERROR(F12/B12,0)</f>
+        <v>-19.70999999999998</v>
       </c>
       <c r="H12">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M,"&lt;0")),0)</f>
         <v>0</v>
       </c>
       <c r="I12">
+        <f>IFERROR(F12/B12,0)</f>
+        <v>-19.70999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <f>COUNTIF(Trades!E:E,A13)</f>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(Trades!E:E, A13,Trades!M:M, "&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f>COUNTIFS(Trades!E:E, A13, Trades!M:M, "&lt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>SUMIF(Trades!E:E,A13,Trades!M:M)</f>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A13, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A13, Trades!M:M,"&lt;0")),0)</f>
+        <v>0</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2582,11 +2904,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9BEB4E-7DDA-44EB-AEDC-C293E2BD344F}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="85.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="172.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2649,12 +2971,52 @@
         <v>82</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5">
+        <v>-19.71</v>
+      </c>
+      <c r="F5" t="s">
+        <v>128</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C1048576" xr:uid="{E90ED070-6DC6-4337-8AA1-210BB22EB913}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C1048576" xr:uid="{E90ED070-6DC6-4337-8AA1-210BB22EB913}">
       <formula1>"Emotiona,Technical"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3" xr:uid="{88B7214E-8E9D-4081-B0FD-1297110AC3FE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C5" xr:uid="{88B7214E-8E9D-4081-B0FD-1297110AC3FE}">
       <formula1>"Emotional,Technical"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{755AB45C-937B-4D2F-B341-462975D65465}">
@@ -2667,7 +3029,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F59AA8-1460-4395-A15C-3B2C7C158D6A}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -2828,8 +3190,8 @@
       <c r="E5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="4">
-        <v>46147</v>
+      <c r="F5" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>94</v>
@@ -2842,6 +3204,34 @@
       </c>
       <c r="J5" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B6">
+        <v>8855</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B7">
+        <v>8784</v>
       </c>
     </row>
   </sheetData>
@@ -2865,7 +3255,7 @@
       </c>
       <c r="B2">
         <f>COUNTA(Trades!A:A)-1</f>
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2874,7 +3264,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Trades!M:M,"&gt;0")/COUNT(Trades!M:M)</f>
-        <v>0.23529411764705882</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2883,7 +3273,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>0.10076470588236992</v>
+        <v>-2.8958499999999852</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2892,7 +3282,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>1.7130000000002887</v>
+        <v>-57.916999999999703</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2901,7 +3291,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>99.731465265599184</v>
+        <v>2.9670045064489021</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2933,7 +3323,7 @@
       </c>
       <c r="B11">
         <f>AVERAGEIF(Trades!M:M,"&gt;0")</f>
-        <v>42.710000000000051</v>
+        <v>34.368000000000038</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2942,7 +3332,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-24.160999999999991</v>
+        <v>-22.975699999999989</v>
       </c>
     </row>
   </sheetData>

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7CB5E2-04F4-465A-82C7-7FAAA2F72F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F5A85E-D877-461E-A8D4-756109CCE78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="150">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -431,6 +431,69 @@
   </si>
   <si>
     <t>The market is really choppy and I didn't wait for confirmation, at the end, what it was looking as a potential bounce, finish by falling back, and not recovering.</t>
+  </si>
+  <si>
+    <t>T-013</t>
+  </si>
+  <si>
+    <t>T-017</t>
+  </si>
+  <si>
+    <t>ROST</t>
+  </si>
+  <si>
+    <t>FROG</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>T-023</t>
+  </si>
+  <si>
+    <t>T-022</t>
+  </si>
+  <si>
+    <t>BBY</t>
+  </si>
+  <si>
+    <t>T-024</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>TSN</t>
+  </si>
+  <si>
+    <t>T-025</t>
+  </si>
+  <si>
+    <t>NUE</t>
+  </si>
+  <si>
+    <t>T-028</t>
+  </si>
+  <si>
+    <t>T-006</t>
+  </si>
+  <si>
+    <t>LGN</t>
+  </si>
+  <si>
+    <t>T-029</t>
+  </si>
+  <si>
+    <t>AGX</t>
+  </si>
+  <si>
+    <t>T-030</t>
+  </si>
+  <si>
+    <t>WMT</t>
+  </si>
+  <si>
+    <t>T-010</t>
   </si>
 </sst>
 </file>
@@ -477,7 +540,75 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -835,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -889,7 +1020,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A21" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
+        <f t="shared" ref="A2:A32" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
         <v>T-001</v>
       </c>
       <c r="B2" s="1">
@@ -1150,11 +1281,11 @@
         <v>32.759999999999962</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M7">
         <f>SUMIF(Executions!B:B,A7,Executions!H:H)</f>
-        <v>0</v>
+        <v>-14.309999999999988</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1334,7 +1465,7 @@
       </c>
       <c r="M11">
         <f>SUMIF(Executions!B:B,A11,Executions!H:H)</f>
-        <v>0</v>
+        <v>4.0500000000000096</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1465,11 +1596,11 @@
         <v>45.779999999999973</v>
       </c>
       <c r="L14" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M14">
         <f>SUMIF(Executions!B:B,A14,Executions!H:H)</f>
-        <v>0</v>
+        <v>-23.430000000000007</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1589,14 +1720,14 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I21" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
+        <f t="shared" ref="I17:I32" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
         <v>10.280000000000001</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17">
-        <f t="shared" ref="K17:K21" si="4">I17*J17</f>
+        <f t="shared" ref="K17:K26" si="4">I17*J17</f>
         <v>20.560000000000002</v>
       </c>
       <c r="L17" t="s">
@@ -1645,11 +1776,11 @@
         <v>113.60000000000014</v>
       </c>
       <c r="L18" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M18">
         <f>SUMIF(Executions!B:B,A18,Executions!H:H)</f>
-        <v>0</v>
+        <v>-83.800000000000239</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1787,23 +1918,521 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f t="shared" si="0"/>
+        <v>T-021</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22">
+        <v>215.7</v>
+      </c>
+      <c r="G22">
+        <v>208.95</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="3"/>
+        <v>13.5</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="L22" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22">
+        <f>SUMIF(Executions!B:B,A22,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f t="shared" si="0"/>
+        <v>T-022</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23">
+        <v>46.58</v>
+      </c>
+      <c r="G23">
+        <v>45.93</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="3"/>
+        <v>1.9499999999999957</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="4"/>
+        <v>1.9499999999999957</v>
+      </c>
+      <c r="L23" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23">
+        <f>SUMIF(Executions!B:B,A23,Executions!H:H)</f>
+        <v>2.5799999999999983</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="str">
+        <f t="shared" si="0"/>
+        <v>T-023</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24">
+        <v>217.51</v>
+      </c>
+      <c r="G24">
+        <v>216.51</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="L24" t="s">
+        <v>75</v>
+      </c>
+      <c r="M24">
+        <f>SUMIF(Executions!B:B,A24,Executions!H:H)</f>
+        <v>3.9800000000000182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f t="shared" si="0"/>
+        <v>T-024</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C25" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25">
+        <v>64.56</v>
+      </c>
+      <c r="G25">
+        <v>63.69</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="3"/>
+        <v>2.6100000000000136</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="4"/>
+        <v>5.2200000000000273</v>
+      </c>
+      <c r="L25" t="s">
+        <v>75</v>
+      </c>
+      <c r="M25">
+        <f>SUMIF(Executions!B:B,A25,Executions!H:H)</f>
+        <v>-2.5500000000000043</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="str">
+        <f t="shared" si="0"/>
+        <v>T-025</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26">
+        <v>159.59</v>
+      </c>
+      <c r="G26">
+        <v>157.08000000000001</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="3"/>
+        <v>5.0199999999999818</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="4"/>
+        <v>10.039999999999964</v>
+      </c>
+      <c r="L26" t="s">
+        <v>75</v>
+      </c>
+      <c r="M26">
+        <f>SUMIF(Executions!B:B,A26,Executions!H:H)</f>
+        <v>-4.8799999999999955</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f t="shared" si="0"/>
+        <v>T-026</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27">
+        <v>63.01</v>
+      </c>
+      <c r="G27">
+        <v>61.7</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>3.9299999999999855</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <f t="shared" ref="K27:K31" si="5">I27*J27</f>
+        <v>3.9299999999999855</v>
+      </c>
+      <c r="L27" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27">
+        <f>SUMIF(Executions!B:B,A27,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="str">
+        <f t="shared" si="0"/>
+        <v>T-027</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28">
+        <v>166.95</v>
+      </c>
+      <c r="G28">
+        <v>159.75</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="3"/>
+        <v>14.399999999999977</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="5"/>
+        <v>28.799999999999955</v>
+      </c>
+      <c r="L28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28">
+        <f>SUMIF(Executions!B:B,A28,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="str">
+        <f t="shared" si="0"/>
+        <v>T-028</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29">
+        <v>157.47</v>
+      </c>
+      <c r="G29">
+        <v>155.03</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="3"/>
+        <v>4.8799999999999955</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="5"/>
+        <v>4.8799999999999955</v>
+      </c>
+      <c r="L29" t="s">
+        <v>75</v>
+      </c>
+      <c r="M29">
+        <f>SUMIF(Executions!B:B,A29,Executions!H:H)</f>
+        <v>-3.3799999999999955</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="str">
+        <f t="shared" si="0"/>
+        <v>T-029</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30">
+        <v>54.44</v>
+      </c>
+      <c r="G30">
+        <v>53.43</v>
+      </c>
+      <c r="H30">
+        <v>4</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="3"/>
+        <v>4.039999999999992</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="5"/>
+        <v>4.039999999999992</v>
+      </c>
+      <c r="L30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M30">
+        <f>SUMIF(Executions!B:B,A30,Executions!H:H)</f>
+        <v>-4.7199999999999989</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="str">
+        <f t="shared" si="0"/>
+        <v>T-030</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31">
+        <v>544.05999999999995</v>
+      </c>
+      <c r="G31">
+        <v>535.73</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="3"/>
+        <v>16.659999999999854</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="5"/>
+        <v>16.659999999999854</v>
+      </c>
+      <c r="L31" t="s">
+        <v>75</v>
+      </c>
+      <c r="M31">
+        <f>SUMIF(Executions!B:B,A31,Executions!H:H)</f>
+        <v>-26.839999999999918</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="str">
+        <f t="shared" si="0"/>
+        <v>T-031</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C32" t="s">
+        <v>148</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32">
+        <v>123.25</v>
+      </c>
+      <c r="G32">
+        <v>120.99</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="3"/>
+        <v>6.7800000000000153</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32">
+        <f t="shared" ref="K32" si="6">I32*J32</f>
+        <v>13.560000000000031</v>
+      </c>
+      <c r="L32" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32">
+        <f>SUMIF(Executions!B:B,A32,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M21">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="M2:M32">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
       <formula>K2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>K2</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7CC3C28F-4F55-4478-BFCD-3E2D4B39BBC5}">
       <formula1>"Long,Short"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E22:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E33:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
       <formula1>"Breakout,Pullback,Range Break,Reversal,Earning Play, A+ Setup,Buy the Dip, Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{F4069621-A7E8-45FE-9BEB-689DCD314A70}">
@@ -1814,12 +2443,12 @@
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F958648C-BDD0-4279-9367-17373A7E8527}">
           <x14:formula1>
             <xm:f>Setups!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E21</xm:sqref>
+          <xm:sqref>E3:E32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35AFC476-A1FB-4896-88D9-082697747CAE}">
           <x14:formula1>
@@ -1835,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -1907,7 +2536,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A17" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A28" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2312,8 +2941,9 @@
       <c r="C15" s="1">
         <v>46099</v>
       </c>
-      <c r="D15" t="s">
-        <v>123</v>
+      <c r="D15" t="str">
+        <f>VLOOKUP(B15,Trades!A$1:M100013,3,FALSE)</f>
+        <v>QBTS</v>
       </c>
       <c r="E15" t="s">
         <v>64</v>
@@ -2344,8 +2974,9 @@
       <c r="C16" s="1">
         <v>46100</v>
       </c>
-      <c r="D16" t="s">
-        <v>114</v>
+      <c r="D16" t="str">
+        <f>VLOOKUP(B16,Trades!A$1:M100014,3,FALSE)</f>
+        <v>AVBP</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -2376,8 +3007,9 @@
       <c r="C17" s="1">
         <v>46101</v>
       </c>
-      <c r="D17" t="s">
-        <v>114</v>
+      <c r="D17" t="str">
+        <f>VLOOKUP(B17,Trades!A$1:M100015,3,FALSE)</f>
+        <v>BDX</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
@@ -2397,12 +3029,375 @@
         <v>-1.9173151750972741</v>
       </c>
     </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46105</v>
+      </c>
+      <c r="D18" t="str">
+        <f>VLOOKUP(B18,Trades!A$1:M100016,3,FALSE)</f>
+        <v>KTOS</v>
+      </c>
+      <c r="E18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18">
+        <v>80.77</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18">
+        <f>IF(VLOOKUP(B18,Trades!A:M,4,FALSE)="Long",(F18-VLOOKUP(B18,Trades!A:M,6,FALSE))*G18,(VLOOKUP(B18,Trades!A:M,6,FALSE)-F18)*G18)</f>
+        <v>-23.430000000000007</v>
+      </c>
+      <c r="I18">
+        <f>H18/Trades!I18</f>
+        <v>-0.41249999999999964</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46105</v>
+      </c>
+      <c r="D19" t="str">
+        <f>VLOOKUP(B19,Trades!A$1:M100017,3,FALSE)</f>
+        <v>MNST</v>
+      </c>
+      <c r="E19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19">
+        <v>72.959999999999994</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <f>IF(VLOOKUP(B19,Trades!A:M,4,FALSE)="Long",(F19-VLOOKUP(B19,Trades!A:M,6,FALSE))*G19,(VLOOKUP(B19,Trades!A:M,6,FALSE)-F19)*G19)</f>
+        <v>-83.800000000000239</v>
+      </c>
+      <c r="I19">
+        <f>H19/Trades!I19</f>
+        <v>-4.5126548196015221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46106</v>
+      </c>
+      <c r="D20" t="str">
+        <f>VLOOKUP(B20,Trades!A$1:M100018,3,FALSE)</f>
+        <v>AMD</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20">
+        <v>219.5</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <f>IF(VLOOKUP(B20,Trades!A:M,4,FALSE)="Long",(F20-VLOOKUP(B20,Trades!A:M,6,FALSE))*G20,(VLOOKUP(B20,Trades!A:M,6,FALSE)-F20)*G20)</f>
+        <v>3.9800000000000182</v>
+      </c>
+      <c r="I20">
+        <f>H20/Trades!I20</f>
+        <v>0.1269132653061231</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46106</v>
+      </c>
+      <c r="D21" t="str">
+        <f>VLOOKUP(B21,Trades!A$1:M100019,3,FALSE)</f>
+        <v>FROG</v>
+      </c>
+      <c r="E21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21">
+        <v>47.87</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <f>IF(VLOOKUP(B21,Trades!A:M,4,FALSE)="Long",(F21-VLOOKUP(B21,Trades!A:M,6,FALSE))*G21,(VLOOKUP(B21,Trades!A:M,6,FALSE)-F21)*G21)</f>
+        <v>2.5799999999999983</v>
+      </c>
+      <c r="I21">
+        <f>H21/Trades!I21</f>
+        <v>0.40062111801242223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46107</v>
+      </c>
+      <c r="D22" t="str">
+        <f>VLOOKUP(B22,Trades!A$1:M100020,3,FALSE)</f>
+        <v>BBY</v>
+      </c>
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22">
+        <v>63.71</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <f>IF(VLOOKUP(B22,Trades!A:M,4,FALSE)="Long",(F22-VLOOKUP(B22,Trades!A:M,6,FALSE))*G22,(VLOOKUP(B22,Trades!A:M,6,FALSE)-F22)*G22)</f>
+        <v>-2.5500000000000043</v>
+      </c>
+      <c r="I22">
+        <f>H22/Trades!I22</f>
+        <v>-0.18888888888888922</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46107</v>
+      </c>
+      <c r="D23" t="str">
+        <f>VLOOKUP(B23,Trades!A$1:M100021,3,FALSE)</f>
+        <v>ARM</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23">
+        <v>157.15</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <f>IF(VLOOKUP(B23,Trades!A:M,4,FALSE)="Long",(F23-VLOOKUP(B23,Trades!A:M,6,FALSE))*G23,(VLOOKUP(B23,Trades!A:M,6,FALSE)-F23)*G23)</f>
+        <v>-4.8799999999999955</v>
+      </c>
+      <c r="I23">
+        <f>H23/Trades!I23</f>
+        <v>-2.5025641025641057</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46107</v>
+      </c>
+      <c r="D24" t="str">
+        <f>VLOOKUP(B24,Trades!A$1:M100022,3,FALSE)</f>
+        <v>ARM</v>
+      </c>
+      <c r="E24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24">
+        <v>155.78</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <f>IF(VLOOKUP(B24,Trades!A:M,4,FALSE)="Long",(F24-VLOOKUP(B24,Trades!A:M,6,FALSE))*G24,(VLOOKUP(B24,Trades!A:M,6,FALSE)-F24)*G24)</f>
+        <v>-3.3799999999999955</v>
+      </c>
+      <c r="I24">
+        <f>H24/Trades!I24</f>
+        <v>-1.1266666666666652</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D25" t="str">
+        <f>VLOOKUP(B25,Trades!A$1:M100023,3,FALSE)</f>
+        <v>ROKU</v>
+      </c>
+      <c r="E25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25">
+        <v>87.72</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <f>IF(VLOOKUP(B25,Trades!A:M,4,FALSE)="Long",(F25-VLOOKUP(B25,Trades!A:M,6,FALSE))*G25,(VLOOKUP(B25,Trades!A:M,6,FALSE)-F25)*G25)</f>
+        <v>-14.309999999999988</v>
+      </c>
+      <c r="I25">
+        <f>H25/Trades!I25</f>
+        <v>-5.4827586206896219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D26" t="str">
+        <f>VLOOKUP(B26,Trades!A$1:M100024,3,FALSE)</f>
+        <v>LGN</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26">
+        <v>53.26</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26">
+        <f>IF(VLOOKUP(B26,Trades!A:M,4,FALSE)="Long",(F26-VLOOKUP(B26,Trades!A:M,6,FALSE))*G26,(VLOOKUP(B26,Trades!A:M,6,FALSE)-F26)*G26)</f>
+        <v>-4.7199999999999989</v>
+      </c>
+      <c r="I26">
+        <f>H26/Trades!I26</f>
+        <v>-0.94023904382470436</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D27" t="str">
+        <f>VLOOKUP(B27,Trades!A$1:M100025,3,FALSE)</f>
+        <v>AGX</v>
+      </c>
+      <c r="E27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27">
+        <v>530.64</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+      <c r="H27">
+        <f>IF(VLOOKUP(B27,Trades!A:M,4,FALSE)="Long",(F27-VLOOKUP(B27,Trades!A:M,6,FALSE))*G27,(VLOOKUP(B27,Trades!A:M,6,FALSE)-F27)*G27)</f>
+        <v>-26.839999999999918</v>
+      </c>
+      <c r="I27">
+        <f>H27/Trades!I27</f>
+        <v>-6.829516539440208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46108</v>
+      </c>
+      <c r="D28" t="str">
+        <f>VLOOKUP(B28,Trades!A$1:M100026,3,FALSE)</f>
+        <v>NRT</v>
+      </c>
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28">
+        <v>9.14</v>
+      </c>
+      <c r="G28">
+        <v>27</v>
+      </c>
+      <c r="H28">
+        <f>IF(VLOOKUP(B28,Trades!A:M,4,FALSE)="Long",(F28-VLOOKUP(B28,Trades!A:M,6,FALSE))*G28,(VLOOKUP(B28,Trades!A:M,6,FALSE)-F28)*G28)</f>
+        <v>4.0500000000000096</v>
+      </c>
+      <c r="I28">
+        <f>H28/Trades!I28</f>
+        <v>0.28125000000000111</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E18:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100017</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E29:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100028</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E17" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E28" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2533,7 +3528,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Trades!E:E,A4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <f>COUNTIFS(Trades!E:E, A4,Trades!M:M, "&gt;0")</f>
@@ -2541,7 +3536,7 @@
       </c>
       <c r="D4">
         <f>COUNTIFS(Trades!E:E, A4, Trades!M:M, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
@@ -2549,11 +3544,11 @@
       </c>
       <c r="F4">
         <f>SUMIF(Trades!E:E,A4,Trades!M:M)</f>
-        <v>0</v>
+        <v>-26.839999999999918</v>
       </c>
       <c r="G4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-26.839999999999918</v>
       </c>
       <c r="H4">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A4, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A4, Trades!M:M,"&lt;0")),0)</f>
@@ -2561,7 +3556,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-26.839999999999918</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2578,7 +3573,7 @@
       </c>
       <c r="D5">
         <f>COUNTIFS(Trades!E:E, A5, Trades!M:M, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
@@ -2586,11 +3581,11 @@
       </c>
       <c r="F5">
         <f>SUMIF(Trades!E:E,A5,Trades!M:M)</f>
-        <v>0</v>
+        <v>-14.309999999999988</v>
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-14.309999999999988</v>
       </c>
       <c r="H5">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A5, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A5, Trades!M:M,"&lt;0")),0)</f>
@@ -2598,7 +3593,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-14.309999999999988</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -2689,7 +3684,7 @@
       </c>
       <c r="D8">
         <f>COUNTIFS(Trades!E:E, A8, Trades!M:M, "&lt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
@@ -2697,11 +3692,11 @@
       </c>
       <c r="F8">
         <f>SUMIF(Trades!E:E,A8,Trades!M:M)</f>
-        <v>0</v>
+        <v>-83.800000000000239</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-83.800000000000239</v>
       </c>
       <c r="H8">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A8, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A8, Trades!M:M,"&lt;0")),0)</f>
@@ -2709,7 +3704,7 @@
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-83.800000000000239</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -2718,35 +3713,35 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Trades!E:E,A9)</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <f>COUNTIFS(Trades!E:E, A9,Trades!M:M, "&gt;0")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <f>COUNTIFS(Trades!E:E, A9, Trades!M:M, "&lt;0")</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.42857142857142855</v>
+        <v>0.3125</v>
       </c>
       <c r="F9">
         <f>SUMIF(Trades!E:E,A9,Trades!M:M)</f>
-        <v>62.665000000000028</v>
+        <v>31.735000000000056</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>8.9521428571428618</v>
+        <v>1.9834375000000035</v>
       </c>
       <c r="H9">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M,"&lt;0")),0)</f>
-        <v>3.4627628217724506</v>
+        <v>1.49274124679761</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>8.9521428571428618</v>
+        <v>1.9834375000000035</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2755,11 +3750,11 @@
       </c>
       <c r="B10">
         <f>COUNTIF(Trades!E:E,A10)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <f>COUNTIFS(Trades!E:E, A10,Trades!M:M, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <f>COUNTIFS(Trades!E:E, A10, Trades!M:M, "&lt;0")</f>
@@ -2767,23 +3762,23 @@
       </c>
       <c r="E10">
         <f>IFERROR(C10/B10,0)</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="F10">
         <f>SUMIF(Trades!E:E,A10,Trades!M:M)</f>
-        <v>-140.0319999999999</v>
+        <v>-137.45199999999988</v>
       </c>
       <c r="G10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-23.338666666666651</v>
+        <v>-19.635999999999985</v>
       </c>
       <c r="H10">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A10, Trades!M:M,"&lt;0")),0)</f>
-        <v>0</v>
+        <v>1.8424360146252285E-2</v>
       </c>
       <c r="I10">
         <f>IFERROR(F10/B10,0)</f>
-        <v>-23.338666666666651</v>
+        <v>-19.635999999999985</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -3255,7 +4250,7 @@
       </c>
       <c r="B2">
         <f>COUNTA(Trades!A:A)-1</f>
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3264,7 +4259,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Trades!M:M,"&gt;0")/COUNT(Trades!M:M)</f>
-        <v>0.25</v>
+        <v>0.25806451612903225</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3273,7 +4268,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>-2.8958499999999852</v>
+        <v>-6.8134516129032203</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3282,7 +4277,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>-57.916999999999703</v>
+        <v>-211.21699999999984</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3291,7 +4286,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>2.9670045064489021</v>
+        <v>0.86380357641667271</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3314,7 +4309,7 @@
       </c>
       <c r="B10">
         <f>MIN(Trades!M:M)</f>
-        <v>-35.010000000000005</v>
+        <v>-83.800000000000239</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3323,7 +4318,7 @@
       </c>
       <c r="B11">
         <f>AVERAGEIF(Trades!M:M,"&gt;0")</f>
-        <v>34.368000000000038</v>
+        <v>22.806250000000027</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3332,7 +4327,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-22.975699999999989</v>
+        <v>-21.87038888888889</v>
       </c>
     </row>
   </sheetData>

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F5A85E-D877-461E-A8D4-756109CCE78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4A1877-BF39-4AFD-B886-EF94DAE0B5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <sheet name="Daily Journal" sheetId="5" r:id="rId5"/>
     <sheet name="Dashboard" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Trades!$L$1:$L$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="160">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -494,6 +497,36 @@
   </si>
   <si>
     <t>T-010</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>T-020</t>
+  </si>
+  <si>
+    <t>T-032</t>
+  </si>
+  <si>
+    <t>UEC</t>
+  </si>
+  <si>
+    <t>CENX</t>
+  </si>
+  <si>
+    <t>T-034</t>
+  </si>
+  <si>
+    <t>PZG</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>T-037</t>
+  </si>
+  <si>
+    <t>T-026</t>
   </si>
 </sst>
 </file>
@@ -540,72 +573,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -966,7 +938,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
-  <dimension ref="A1:M32"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -1018,9 +991,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A32" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
+        <f t="shared" ref="A2:A38" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
         <v>T-001</v>
       </c>
       <c r="B2" s="1">
@@ -1063,7 +1036,7 @@
         <v>-23.399999999999981</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f t="shared" si="0"/>
         <v>T-002</v>
@@ -1108,7 +1081,7 @@
         <v>6.7100000000000195</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f t="shared" si="0"/>
         <v>T-003</v>
@@ -1153,7 +1126,7 @@
         <v>-35.010000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>T-004</v>
@@ -1191,14 +1164,14 @@
         <v>49.679999999999993</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M5">
         <f>SUMIF(Executions!B:B,A5,Executions!H:H)</f>
         <v>59.310000000000031</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>T-005</v>
@@ -1243,7 +1216,7 @@
         <v>-10.601999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>T-006</v>
@@ -1288,7 +1261,7 @@
         <v>-14.309999999999988</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>T-007</v>
@@ -1333,7 +1306,7 @@
         <v>-28.16999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>T-008</v>
@@ -1378,7 +1351,7 @@
         <v>80.400000000000034</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>T-009</v>
@@ -1423,7 +1396,7 @@
         <v>-25.445000000000011</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>T-010</v>
@@ -1468,7 +1441,7 @@
         <v>4.0500000000000096</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>T-011</v>
@@ -1513,7 +1486,7 @@
         <v>24.42000000000013</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>T-012</v>
@@ -1558,7 +1531,7 @@
         <v>-24.779999999999976</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>T-013</v>
@@ -1603,7 +1576,7 @@
         <v>-23.430000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>T-014</v>
@@ -1648,7 +1621,7 @@
         <v>-21.71999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>T-015</v>
@@ -1693,7 +1666,7 @@
         <v>0.99999999999997868</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>T-016</v>
@@ -1720,7 +1693,7 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I32" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
+        <f t="shared" ref="I17:I35" si="3">IF(D17="Long",(F17-G17)*H17,(G17-F17)*0)</f>
         <v>10.280000000000001</v>
       </c>
       <c r="J17">
@@ -1731,14 +1704,14 @@
         <v>20.560000000000002</v>
       </c>
       <c r="L17" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M17">
         <f>SUMIF(Executions!B:B,A17,Executions!H:H)</f>
         <v>-9.5600000000000023</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>T-017</v>
@@ -1783,7 +1756,7 @@
         <v>-83.800000000000239</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>T-018</v>
@@ -1828,7 +1801,7 @@
         <v>-19.70999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>T-019</v>
@@ -1873,7 +1846,7 @@
         <v>-31.359999999999985</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>T-020</v>
@@ -1911,11 +1884,11 @@
         <v>12.879999999999995</v>
       </c>
       <c r="L21" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M21">
         <f>SUMIF(Executions!B:B,A21,Executions!H:H)</f>
-        <v>0</v>
+        <v>36.119999999999976</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -1963,7 +1936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>T-022</v>
@@ -2008,7 +1981,7 @@
         <v>2.5799999999999983</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>T-023</v>
@@ -2053,7 +2026,7 @@
         <v>3.9800000000000182</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>T-024</v>
@@ -2098,7 +2071,7 @@
         <v>-2.5500000000000043</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>T-025</v>
@@ -2181,11 +2154,11 @@
         <v>3.9299999999999855</v>
       </c>
       <c r="L27" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M27">
         <f>SUMIF(Executions!B:B,A27,Executions!H:H)</f>
-        <v>0</v>
+        <v>3.1500000000000128</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -2233,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>T-028</v>
@@ -2278,7 +2251,7 @@
         <v>-3.3799999999999955</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>T-029</v>
@@ -2323,7 +2296,7 @@
         <v>-4.7199999999999989</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>T-030</v>
@@ -2402,7 +2375,7 @@
         <v>2</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32" si="6">I32*J32</f>
+        <f t="shared" ref="K32:K38" si="6">I32*J32</f>
         <v>13.560000000000031</v>
       </c>
       <c r="L32" t="s">
@@ -2413,48 +2386,325 @@
         <v>0</v>
       </c>
     </row>
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f t="shared" si="0"/>
+        <v>T-032</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33">
+        <v>62.92</v>
+      </c>
+      <c r="G33">
+        <v>61.92</v>
+      </c>
+      <c r="H33">
+        <v>3</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="L33" t="s">
+        <v>75</v>
+      </c>
+      <c r="M33">
+        <f>SUMIF(Executions!B:B,A33,Executions!H:H)</f>
+        <v>7.9799999999999898</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="str">
+        <f t="shared" si="0"/>
+        <v>T-033</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C34" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34">
+        <v>13.07</v>
+      </c>
+      <c r="G34">
+        <v>12.24</v>
+      </c>
+      <c r="H34">
+        <v>14</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="3"/>
+        <v>11.620000000000001</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="6"/>
+        <v>11.620000000000001</v>
+      </c>
+      <c r="L34" t="s">
+        <v>30</v>
+      </c>
+      <c r="M34">
+        <f>SUMIF(Executions!B:B,A34,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f t="shared" si="0"/>
+        <v>T-034</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C35" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35">
+        <v>58.53</v>
+      </c>
+      <c r="G35">
+        <v>57.53</v>
+      </c>
+      <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="L35" t="s">
+        <v>75</v>
+      </c>
+      <c r="M35">
+        <f>SUMIF(Executions!B:B,A35,Executions!H:H)</f>
+        <v>-3.9200000000000159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="str">
+        <f t="shared" si="0"/>
+        <v>T-035</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36">
+        <v>156.61000000000001</v>
+      </c>
+      <c r="G36">
+        <v>153.01</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36">
+        <f>IF(D36="Long",(F36-G36)*H36,(G36-F36)*0)</f>
+        <v>10.800000000000068</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="6"/>
+        <v>10.800000000000068</v>
+      </c>
+      <c r="L36" t="s">
+        <v>30</v>
+      </c>
+      <c r="M36">
+        <f>SUMIF(Executions!B:B,A36,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="str">
+        <f t="shared" si="0"/>
+        <v>T-036</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C37" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37">
+        <v>1.69</v>
+      </c>
+      <c r="G37">
+        <v>1.48</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <f>IF(D37="Long",(F37-G37)*H37,(G37-F37)*0)</f>
+        <v>20.999999999999996</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="6"/>
+        <v>20.999999999999996</v>
+      </c>
+      <c r="L37" t="s">
+        <v>30</v>
+      </c>
+      <c r="M37">
+        <f>SUMIF(Executions!B:B,A37,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="str">
+        <f t="shared" si="0"/>
+        <v>T-037</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46113</v>
+      </c>
+      <c r="C38" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38">
+        <v>292.51</v>
+      </c>
+      <c r="G38">
+        <v>291.02</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38">
+        <f>IF(D38="Long",(F38-G38)*H38,(G38-F38)*0)</f>
+        <v>2.9800000000000182</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="6"/>
+        <v>2.9800000000000182</v>
+      </c>
+      <c r="L38" t="s">
+        <v>75</v>
+      </c>
+      <c r="M38">
+        <f>SUMIF(Executions!B:B,A38,Executions!H:H)</f>
+        <v>4.32000000000005</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M32">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+  <autoFilter ref="L1:L35" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Open"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="M2:M38">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
       <formula>K2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="lessThan">
       <formula>K2</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7CC3C28F-4F55-4478-BFCD-3E2D4B39BBC5}">
-      <formula1>"Long,Short"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E33:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E39:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
       <formula1>"Breakout,Pullback,Range Break,Reversal,Earning Play, A+ Setup,Buy the Dip, Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{F4069621-A7E8-45FE-9BEB-689DCD314A70}">
       <formula1>"Open,Closed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7CC3C28F-4F55-4478-BFCD-3E2D4B39BBC5}">
+      <formula1>"Long,Short"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F958648C-BDD0-4279-9367-17373A7E8527}">
-          <x14:formula1>
-            <xm:f>Setups!$A$2:$A$13</xm:f>
-          </x14:formula1>
-          <xm:sqref>E3:E32</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35AFC476-A1FB-4896-88D9-082697747CAE}">
           <x14:formula1>
             <xm:f>Setups!$A$2:$A$14</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F958648C-BDD0-4279-9367-17373A7E8527}">
+          <x14:formula1>
+            <xm:f>Setups!$A$2:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>E3:E38</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2464,7 +2714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -2536,7 +2786,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A28" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A33" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -3392,12 +3642,177 @@
         <v>0.28125000000000111</v>
       </c>
     </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D29" t="str">
+        <f>VLOOKUP(B29,Trades!A$1:M100027,3,FALSE)</f>
+        <v>XLE</v>
+      </c>
+      <c r="E29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29">
+        <v>61.86</v>
+      </c>
+      <c r="G29">
+        <v>12</v>
+      </c>
+      <c r="H29">
+        <f>IF(VLOOKUP(B29,Trades!A:M,4,FALSE)="Long",(F29-VLOOKUP(B29,Trades!A:M,6,FALSE))*G29,(VLOOKUP(B29,Trades!A:M,6,FALSE)-F29)*G29)</f>
+        <v>36.119999999999976</v>
+      </c>
+      <c r="I29">
+        <f>H29/Trades!I29</f>
+        <v>7.4016393442622972</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46112</v>
+      </c>
+      <c r="D30" t="str">
+        <f>VLOOKUP(B30,Trades!A$1:M100028,3,FALSE)</f>
+        <v>AA</v>
+      </c>
+      <c r="E30" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30">
+        <v>65.58</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <f>IF(VLOOKUP(B30,Trades!A:M,4,FALSE)="Long",(F30-VLOOKUP(B30,Trades!A:M,6,FALSE))*G30,(VLOOKUP(B30,Trades!A:M,6,FALSE)-F30)*G30)</f>
+        <v>7.9799999999999898</v>
+      </c>
+      <c r="I30">
+        <f>H30/Trades!I30</f>
+        <v>1.9752475247524766</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46112</v>
+      </c>
+      <c r="D31" t="str">
+        <f>VLOOKUP(B31,Trades!A$1:M100029,3,FALSE)</f>
+        <v>CENX</v>
+      </c>
+      <c r="E31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31">
+        <v>57.55</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <f>IF(VLOOKUP(B31,Trades!A:M,4,FALSE)="Long",(F31-VLOOKUP(B31,Trades!A:M,6,FALSE))*G31,(VLOOKUP(B31,Trades!A:M,6,FALSE)-F31)*G31)</f>
+        <v>-3.9200000000000159</v>
+      </c>
+      <c r="I31">
+        <f>H31/Trades!I31</f>
+        <v>-0.23529411764706185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D32" t="str">
+        <f>VLOOKUP(B32,Trades!A$1:M100030,3,FALSE)</f>
+        <v>GOOG</v>
+      </c>
+      <c r="E32" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32">
+        <v>294.67</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <f>IF(VLOOKUP(B32,Trades!A:M,4,FALSE)="Long",(F32-VLOOKUP(B32,Trades!A:M,6,FALSE))*G32,(VLOOKUP(B32,Trades!A:M,6,FALSE)-F32)*G32)</f>
+        <v>4.32000000000005</v>
+      </c>
+      <c r="I32">
+        <f>H32/Trades!I32</f>
+        <v>0.63716814159292634</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46113</v>
+      </c>
+      <c r="D33" t="str">
+        <f>VLOOKUP(B33,Trades!A$1:M100031,3,FALSE)</f>
+        <v>TSN</v>
+      </c>
+      <c r="E33" t="s">
+        <v>64</v>
+      </c>
+      <c r="F33">
+        <v>64.06</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33">
+        <f>IF(VLOOKUP(B33,Trades!A:M,4,FALSE)="Long",(F33-VLOOKUP(B33,Trades!A:M,6,FALSE))*G33,(VLOOKUP(B33,Trades!A:M,6,FALSE)-F33)*G33)</f>
+        <v>3.1500000000000128</v>
+      </c>
+      <c r="I33">
+        <f>H33/Trades!I33</f>
+        <v>1.0500000000000043</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E29:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100028</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E34:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100033</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E28" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E33" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3565,11 +3980,11 @@
       </c>
       <c r="B5">
         <f>COUNTIF(Trades!E:E,A5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <f>COUNTIFS(Trades!E:E, A5,Trades!M:M, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <f>COUNTIFS(Trades!E:E, A5, Trades!M:M, "&lt;0")</f>
@@ -3577,23 +3992,23 @@
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F5">
         <f>SUMIF(Trades!E:E,A5,Trades!M:M)</f>
-        <v>-14.309999999999988</v>
+        <v>-6.3299999999999983</v>
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>-14.309999999999988</v>
+        <v>-2.1099999999999994</v>
       </c>
       <c r="H5">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A5, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A5, Trades!M:M,"&lt;0")),0)</f>
-        <v>0</v>
+        <v>0.55765199161425549</v>
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>-14.309999999999988</v>
+        <v>-2.1099999999999994</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -3713,35 +4128,35 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Trades!E:E,A9)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <f>COUNTIFS(Trades!E:E, A9,Trades!M:M, "&gt;0")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <f>COUNTIFS(Trades!E:E, A9, Trades!M:M, "&lt;0")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.3125</v>
+        <v>0.41176470588235292</v>
       </c>
       <c r="F9">
         <f>SUMIF(Trades!E:E,A9,Trades!M:M)</f>
-        <v>31.735000000000056</v>
+        <v>67.085000000000008</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>1.9834375000000035</v>
+        <v>3.9461764705882358</v>
       </c>
       <c r="H9">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M,"&lt;0")),0)</f>
-        <v>1.49274124679761</v>
+        <v>1.9818514452982074</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>1.9834375000000035</v>
+        <v>3.9461764705882358</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3824,11 +4239,11 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Trades!E:E,A12)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <f>COUNTIFS(Trades!E:E, A12,Trades!M:M, "&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <f>COUNTIFS(Trades!E:E, A12, Trades!M:M, "&lt;0")</f>
@@ -3836,23 +4251,23 @@
       </c>
       <c r="E12">
         <f>IFERROR(C12/B12,0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F12">
         <f>SUMIF(Trades!E:E,A12,Trades!M:M)</f>
-        <v>-19.70999999999998</v>
+        <v>-15.38999999999993</v>
       </c>
       <c r="G12">
         <f>IFERROR(F12/B12,0)</f>
-        <v>-19.70999999999998</v>
+        <v>-3.8474999999999824</v>
       </c>
       <c r="H12">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M,"&lt;0")),0)</f>
-        <v>0</v>
+        <v>0.21917808219178359</v>
       </c>
       <c r="I12">
         <f>IFERROR(F12/B12,0)</f>
-        <v>-19.70999999999998</v>
+        <v>-3.8474999999999824</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4250,7 +4665,7 @@
       </c>
       <c r="B2">
         <f>COUNTA(Trades!A:A)-1</f>
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4259,7 +4674,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Trades!M:M,"&gt;0")/COUNT(Trades!M:M)</f>
-        <v>0.25806451612903225</v>
+        <v>0.32432432432432434</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4268,7 +4683,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>-6.8134516129032203</v>
+        <v>-4.4207297297297243</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4277,7 +4692,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>-211.21699999999984</v>
+        <v>-163.56699999999981</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4286,7 +4701,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>0.86380357641667271</v>
+        <v>1.4307286922178708</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4318,7 +4733,7 @@
       </c>
       <c r="B11">
         <f>AVERAGEIF(Trades!M:M,"&gt;0")</f>
-        <v>22.806250000000027</v>
+        <v>19.501666666666683</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4327,7 +4742,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-21.87038888888889</v>
+        <v>-20.925631578947371</v>
       </c>
     </row>
   </sheetData>

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alonso\Documents\GitHub\Trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4A1877-BF39-4AFD-B886-EF94DAE0B5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6BB3DA-090F-4868-9DF7-11EFEBD2E98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Dashboard" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Trades!$L$1:$L$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Trades!$L$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="163">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -527,6 +527,15 @@
   </si>
   <si>
     <t>T-026</t>
+  </si>
+  <si>
+    <t>XOM</t>
+  </si>
+  <si>
+    <t>T-038</t>
+  </si>
+  <si>
+    <t>LEXX</t>
   </si>
 </sst>
 </file>
@@ -939,7 +948,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -993,7 +1002,7 @@
     </row>
     <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A38" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
+        <f t="shared" ref="A2:A41" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
         <v>T-001</v>
       </c>
       <c r="B2" s="1">
@@ -2116,7 +2125,7 @@
         <v>-4.8799999999999955</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>T-026</v>
@@ -2375,7 +2384,7 @@
         <v>2</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32:K38" si="6">I32*J32</f>
+        <f t="shared" ref="K32:K41" si="6">I32*J32</f>
         <v>13.560000000000031</v>
       </c>
       <c r="L32" t="s">
@@ -2446,7 +2455,7 @@
         <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="F34">
         <v>13.07</v>
@@ -2548,7 +2557,7 @@
         <v>3</v>
       </c>
       <c r="I36">
-        <f>IF(D36="Long",(F36-G36)*H36,(G36-F36)*0)</f>
+        <f t="shared" ref="I36:I41" si="7">IF(D36="Long",(F36-G36)*H36,(G36-F36)*0)</f>
         <v>10.800000000000068</v>
       </c>
       <c r="J36">
@@ -2593,7 +2602,7 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <f>IF(D37="Long",(F37-G37)*H37,(G37-F37)*0)</f>
+        <f t="shared" si="7"/>
         <v>20.999999999999996</v>
       </c>
       <c r="J37">
@@ -2611,7 +2620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
         <v>T-037</v>
@@ -2638,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="I38">
-        <f>IF(D38="Long",(F38-G38)*H38,(G38-F38)*0)</f>
+        <f t="shared" si="7"/>
         <v>2.9800000000000182</v>
       </c>
       <c r="J38">
@@ -2656,15 +2665,150 @@
         <v>4.32000000000005</v>
       </c>
     </row>
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="str">
+        <f t="shared" si="0"/>
+        <v>T-038</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C39" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39">
+        <v>165.58</v>
+      </c>
+      <c r="G39">
+        <v>163.58000000000001</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="L39" t="s">
+        <v>75</v>
+      </c>
+      <c r="M39">
+        <f>SUMIF(Executions!B:B,A39,Executions!H:H)</f>
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="str">
+        <f t="shared" si="0"/>
+        <v>T-039</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C40" t="s">
+        <v>162</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" t="s">
+        <v>61</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40">
+        <v>0.89339999999999997</v>
+      </c>
+      <c r="H40">
+        <v>50</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="7"/>
+        <v>5.3300000000000018</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="6"/>
+        <v>5.3300000000000018</v>
+      </c>
+      <c r="L40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40">
+        <f>SUMIF(Executions!B:B,A40,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="str">
+        <f t="shared" si="0"/>
+        <v>T-040</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46114</v>
+      </c>
+      <c r="C41" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41">
+        <v>72.02</v>
+      </c>
+      <c r="G41">
+        <v>70.430000000000007</v>
+      </c>
+      <c r="H41">
+        <v>6</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="7"/>
+        <v>9.5399999999999352</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="6"/>
+        <v>19.07999999999987</v>
+      </c>
+      <c r="L41" t="s">
+        <v>30</v>
+      </c>
+      <c r="M41">
+        <f>SUMIF(Executions!B:B,A41,Executions!H:H)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="L1:L35" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
+  <autoFilter ref="L1:L39" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
     <filterColumn colId="0">
       <filters>
         <filter val="Open"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="M2:M38">
+  <conditionalFormatting sqref="M2:M41">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -2679,7 +2823,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E39:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E42:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
       <formula1>"Breakout,Pullback,Range Break,Reversal,Earning Play, A+ Setup,Buy the Dip, Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{F4069621-A7E8-45FE-9BEB-689DCD314A70}">
@@ -2704,7 +2848,7 @@
           <x14:formula1>
             <xm:f>Setups!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E38</xm:sqref>
+          <xm:sqref>E3:E41</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2714,7 +2858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -2786,7 +2930,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A33" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A34" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -3807,12 +3951,45 @@
         <v>1.0500000000000043</v>
       </c>
     </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46114</v>
+      </c>
+      <c r="D34" t="str">
+        <f>VLOOKUP(B34,Trades!A$1:M100032,3,FALSE)</f>
+        <v>XOM</v>
+      </c>
+      <c r="E34" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34">
+        <v>163.58000000000001</v>
+      </c>
+      <c r="G34">
+        <v>2</v>
+      </c>
+      <c r="H34">
+        <f>IF(VLOOKUP(B34,Trades!A:M,4,FALSE)="Long",(F34-VLOOKUP(B34,Trades!A:M,6,FALSE))*G34,(VLOOKUP(B34,Trades!A:M,6,FALSE)-F34)*G34)</f>
+        <v>-4</v>
+      </c>
+      <c r="I34">
+        <f>H34/Trades!I34</f>
+        <v>-0.34423407917383819</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E34:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100033</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E35:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100034</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E33" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E34" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3980,7 +4157,7 @@
       </c>
       <c r="B5">
         <f>COUNTIF(Trades!E:E,A5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <f>COUNTIFS(Trades!E:E, A5,Trades!M:M, "&gt;0")</f>
@@ -3992,7 +4169,7 @@
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
         <f>SUMIF(Trades!E:E,A5,Trades!M:M)</f>
@@ -4000,7 +4177,7 @@
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>-2.1099999999999994</v>
+        <v>-3.1649999999999991</v>
       </c>
       <c r="H5">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A5, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A5, Trades!M:M,"&lt;0")),0)</f>
@@ -4008,7 +4185,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>-2.1099999999999994</v>
+        <v>-3.1649999999999991</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -4128,7 +4305,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Trades!E:E,A9)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9">
         <f>COUNTIFS(Trades!E:E, A9,Trades!M:M, "&gt;0")</f>
@@ -4140,7 +4317,7 @@
       </c>
       <c r="E9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.41176470588235292</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="F9">
         <f>SUMIF(Trades!E:E,A9,Trades!M:M)</f>
@@ -4148,7 +4325,7 @@
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>3.9461764705882358</v>
+        <v>3.7269444444444448</v>
       </c>
       <c r="H9">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M,"&lt;0")),0)</f>
@@ -4156,7 +4333,7 @@
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>3.9461764705882358</v>
+        <v>3.7269444444444448</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -4239,7 +4416,7 @@
       </c>
       <c r="B12">
         <f>COUNTIF(Trades!E:E,A12)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <f>COUNTIFS(Trades!E:E, A12,Trades!M:M, "&gt;0")</f>
@@ -4247,27 +4424,27 @@
       </c>
       <c r="D12">
         <f>COUNTIFS(Trades!E:E, A12, Trades!M:M, "&lt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
         <f>IFERROR(C12/B12,0)</f>
-        <v>0.25</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="F12">
         <f>SUMIF(Trades!E:E,A12,Trades!M:M)</f>
-        <v>-15.38999999999993</v>
+        <v>-19.38999999999993</v>
       </c>
       <c r="G12">
         <f>IFERROR(F12/B12,0)</f>
-        <v>-3.8474999999999824</v>
+        <v>-2.7699999999999898</v>
       </c>
       <c r="H12">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M,"&lt;0")),0)</f>
-        <v>0.21917808219178359</v>
+        <v>0.18220160269928526</v>
       </c>
       <c r="I12">
         <f>IFERROR(F12/B12,0)</f>
-        <v>-3.8474999999999824</v>
+        <v>-2.7699999999999898</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4665,7 +4842,7 @@
       </c>
       <c r="B2">
         <f>COUNTA(Trades!A:A)-1</f>
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4674,7 +4851,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Trades!M:M,"&gt;0")/COUNT(Trades!M:M)</f>
-        <v>0.32432432432432434</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4683,7 +4860,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>-4.4207297297297243</v>
+        <v>-4.1891749999999952</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4692,7 +4869,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>-163.56699999999981</v>
+        <v>-167.56699999999981</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4701,7 +4878,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>1.4307286922178708</v>
+        <v>1.3965756980789803</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4742,7 +4919,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-20.925631578947371</v>
+        <v>-20.079350000000002</v>
       </c>
     </row>
   </sheetData>

--- a/New tracking file.xlsx
+++ b/New tracking file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zuriel\Documents\github\Trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6BB3DA-090F-4868-9DF7-11EFEBD2E98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8099ED-9DF8-448A-A442-0C0E43FEE4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{045517DB-0C92-4CAE-B507-36AB229E2600}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Dashboard" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Trades!$L$1:$L$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Trades!$L$1:$L$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="167">
   <si>
     <t>Trade_ID</t>
   </si>
@@ -536,6 +536,18 @@
   </si>
   <si>
     <t>LEXX</t>
+  </si>
+  <si>
+    <t>T-035</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>T-041</t>
+  </si>
+  <si>
+    <t>T-042</t>
   </si>
 </sst>
 </file>
@@ -948,7 +960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
@@ -1002,7 +1014,7 @@
     </row>
     <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f t="shared" ref="A2:A41" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
+        <f t="shared" ref="A2:A43" si="0">"T-"&amp; TEXT(ROW()-1,"000")</f>
         <v>T-001</v>
       </c>
       <c r="B2" s="1">
@@ -2384,7 +2396,7 @@
         <v>2</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32:K41" si="6">I32*J32</f>
+        <f t="shared" ref="K32:K42" si="6">I32*J32</f>
         <v>13.560000000000031</v>
       </c>
       <c r="L32" t="s">
@@ -2530,7 +2542,7 @@
         <v>-3.9200000000000159</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="0"/>
         <v>T-035</v>
@@ -2557,7 +2569,7 @@
         <v>3</v>
       </c>
       <c r="I36">
-        <f t="shared" ref="I36:I41" si="7">IF(D36="Long",(F36-G36)*H36,(G36-F36)*0)</f>
+        <f t="shared" ref="I36:I43" si="7">IF(D36="Long",(F36-G36)*H36,(G36-F36)*0)</f>
         <v>10.800000000000068</v>
       </c>
       <c r="J36">
@@ -2568,11 +2580,11 @@
         <v>10.800000000000068</v>
       </c>
       <c r="L36" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M36">
         <f>SUMIF(Executions!B:B,A36,Executions!H:H)</f>
-        <v>0</v>
+        <v>-11.04000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
@@ -2800,15 +2812,105 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="str">
+        <f t="shared" si="0"/>
+        <v>T-041</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C42" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42">
+        <v>51.72</v>
+      </c>
+      <c r="G42">
+        <v>50.62</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="7"/>
+        <v>4.4000000000000057</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="6"/>
+        <v>4.4000000000000057</v>
+      </c>
+      <c r="L42" t="s">
+        <v>75</v>
+      </c>
+      <c r="M42">
+        <f>SUMIF(Executions!B:B,A42,Executions!H:H)</f>
+        <v>-4.4000000000000057</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" t="str">
+        <f t="shared" si="0"/>
+        <v>T-042</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46118</v>
+      </c>
+      <c r="C43" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43">
+        <v>50.72</v>
+      </c>
+      <c r="G43">
+        <v>50.01</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="7"/>
+        <v>2.8400000000000034</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <f t="shared" ref="K43" si="8">I43*J43</f>
+        <v>5.6800000000000068</v>
+      </c>
+      <c r="L43" t="s">
+        <v>75</v>
+      </c>
+      <c r="M43">
+        <f>SUMIF(Executions!B:B,A43,Executions!H:H)</f>
+        <v>-2.960000000000008</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="L1:L39" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
+  <autoFilter ref="L1:L43" xr:uid="{BD04ADA4-A6CF-4E94-AECD-A49BC2D74812}">
     <filterColumn colId="0">
       <filters>
         <filter val="Open"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="M2:M41">
+  <conditionalFormatting sqref="M2:M43">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -2823,7 +2925,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E42:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1 E44:E1048576" xr:uid="{184E1B61-3233-4303-B854-3059829C2393}">
       <formula1>"Breakout,Pullback,Range Break,Reversal,Earning Play, A+ Setup,Buy the Dip, Other"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{F4069621-A7E8-45FE-9BEB-689DCD314A70}">
@@ -2848,7 +2950,7 @@
           <x14:formula1>
             <xm:f>Setups!$A$2:$A$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E41</xm:sqref>
+          <xm:sqref>E3:E43</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2858,7 +2960,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFD56475-86FC-4B41-8DB1-3EDC95E09B14}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -2930,7 +3032,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f t="shared" ref="A3:A34" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A37" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -3984,12 +4086,108 @@
         <v>-0.34423407917383819</v>
       </c>
     </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D35" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" t="s">
+        <v>64</v>
+      </c>
+      <c r="F35">
+        <v>152.93</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <f>IF(VLOOKUP(B35,Trades!A:M,4,FALSE)="Long",(F35-VLOOKUP(B35,Trades!A:M,6,FALSE))*G35,(VLOOKUP(B35,Trades!A:M,6,FALSE)-F35)*G35)</f>
+        <v>-11.04000000000002</v>
+      </c>
+      <c r="I35">
+        <f>H35/Trades!I35</f>
+        <v>-2.7600000000000051</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D36" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36">
+        <v>50.62</v>
+      </c>
+      <c r="G36">
+        <v>4</v>
+      </c>
+      <c r="H36">
+        <f>IF(VLOOKUP(B36,Trades!A:M,4,FALSE)="Long",(F36-VLOOKUP(B36,Trades!A:M,6,FALSE))*G36,(VLOOKUP(B36,Trades!A:M,6,FALSE)-F36)*G36)</f>
+        <v>-4.4000000000000057</v>
+      </c>
+      <c r="I36">
+        <f>H36/Trades!I36</f>
+        <v>-0.40740740740740539</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46118</v>
+      </c>
+      <c r="D37" t="s">
+        <v>164</v>
+      </c>
+      <c r="E37" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37">
+        <v>49.98</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="H37">
+        <f>IF(VLOOKUP(B37,Trades!A:M,4,FALSE)="Long",(F37-VLOOKUP(B37,Trades!A:M,6,FALSE))*G37,(VLOOKUP(B37,Trades!A:M,6,FALSE)-F37)*G37)</f>
+        <v>-2.960000000000008</v>
+      </c>
+      <c r="I37">
+        <f>H37/Trades!I37</f>
+        <v>-0.14095238095238136</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E35:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
-      <formula1>$E$2:$E100034</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E38:E1048576" xr:uid="{05958E25-911C-4ED3-A0F6-7B25054B7856}">
+      <formula1>$E$2:$E100037</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E34" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E37" xr:uid="{9C25687B-DEF5-4411-BA9A-40CB4D950704}">
       <formula1>"Sell,Cover"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4305,7 +4503,7 @@
       </c>
       <c r="B9">
         <f>COUNTIF(Trades!E:E,A9)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <f>COUNTIFS(Trades!E:E, A9,Trades!M:M, "&gt;0")</f>
@@ -4313,27 +4511,27 @@
       </c>
       <c r="D9">
         <f>COUNTIFS(Trades!E:E, A9, Trades!M:M, "&lt;0")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.3888888888888889</v>
+        <v>0.35</v>
       </c>
       <c r="F9">
         <f>SUMIF(Trades!E:E,A9,Trades!M:M)</f>
-        <v>67.085000000000008</v>
+        <v>59.724999999999994</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>3.7269444444444448</v>
+        <v>2.9862499999999996</v>
       </c>
       <c r="H9">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A9, Trades!M:M,"&lt;0")),0)</f>
-        <v>1.9818514452982074</v>
+        <v>1.7891259826914183</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>3.7269444444444448</v>
+        <v>2.9862499999999996</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -4424,7 +4622,7 @@
       </c>
       <c r="D12">
         <f>COUNTIFS(Trades!E:E, A12, Trades!M:M, "&lt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <f>IFERROR(C12/B12,0)</f>
@@ -4432,19 +4630,19 @@
       </c>
       <c r="F12">
         <f>SUMIF(Trades!E:E,A12,Trades!M:M)</f>
-        <v>-19.38999999999993</v>
+        <v>-30.42999999999995</v>
       </c>
       <c r="G12">
         <f>IFERROR(F12/B12,0)</f>
-        <v>-2.7699999999999898</v>
+        <v>-4.3471428571428499</v>
       </c>
       <c r="H12">
         <f>IFERROR( SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M, "&gt;0")/ABS(SUMIFS(Trades!M:M, Trades!E:E, A12, Trades!M:M,"&lt;0")),0)</f>
-        <v>0.18220160269928526</v>
+        <v>0.12431654676259137</v>
       </c>
       <c r="I12">
         <f>IFERROR(F12/B12,0)</f>
-        <v>-2.7699999999999898</v>
+        <v>-4.3471428571428499</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4842,7 +5040,7 @@
       </c>
       <c r="B2">
         <f>COUNTA(Trades!A:A)-1</f>
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4851,7 +5049,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF(Trades!M:M,"&gt;0")/COUNT(Trades!M:M)</f>
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4860,7 +5058,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(Trades!M:M)</f>
-        <v>-4.1891749999999952</v>
+        <v>-4.4277857142857107</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4869,7 +5067,7 @@
       </c>
       <c r="B5">
         <f>SUM(Trades!M:M)</f>
-        <v>-167.56699999999981</v>
+        <v>-185.96699999999984</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4878,7 +5076,7 @@
       </c>
       <c r="B6">
         <f>SUMIF(Trades!M:M,"&gt;0")/ABS(SUM(Trades!M:M,""&lt;0))</f>
-        <v>1.3965756980789803</v>
+        <v>1.2583953066942006</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4919,7 +5117,7 @@
       </c>
       <c r="B12">
         <f>AVERAGEIF(Trades!M:M,"&lt;0")</f>
-        <v>-20.079350000000002</v>
+        <v>-18.260304347826089</v>
       </c>
     </row>
   </sheetData>
